--- a/data/trans_camb/P1401-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1401-Provincia-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-1,68</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-0,97</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 0,0</t>
+          <t>-2,72; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,95</t>
+          <t>-2,04; 1,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,98</t>
+          <t>-3,61; 1,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,18</t>
+          <t>-4,5; 0,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,71</t>
+          <t>-2,4; 0,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 0,29</t>
+          <t>-2,59; 0,28</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-31,42%</t>
+          <t>-23,03%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-57,59%</t>
+          <t>-58,27%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-49,7%</t>
+          <t>-47,32%</t>
         </is>
       </c>
     </row>
@@ -712,27 +712,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-97,75; 272,59</t>
+          <t>-99,33; 346,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,73; 143,71</t>
+          <t>-80,82; 126,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-86,98; 19,35</t>
+          <t>-86,77; 46,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,95; 72,25</t>
+          <t>-76,14; 80,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,24; 39,9</t>
+          <t>-79,31; 28,55</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,71</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,23</t>
+          <t>-0,97; 1,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,88</t>
+          <t>-0,27; 2,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,85</t>
+          <t>-1,96; 0,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,62</t>
+          <t>-1,23; 1,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,64</t>
+          <t>-1,05; 0,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,85</t>
+          <t>-0,35; 1,73</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>159,8%</t>
+          <t>150,95%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,16; 666,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 999,51</t>
+          <t>-39,38; 910,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 212,56</t>
+          <t>-91,12; 242,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-60,73; 319,42</t>
+          <t>-61,42; 294,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,62; 132,35</t>
+          <t>-69,25; 143,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 317,38</t>
+          <t>-30,7; 288,06</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 1,76</t>
+          <t>-2,74; 1,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 2,08</t>
+          <t>-2,51; 2,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 5,44</t>
+          <t>-0,56; 4,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,49</t>
+          <t>-1,02; 2,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,66</t>
+          <t>-0,83; 2,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,8</t>
+          <t>-0,97; 1,87</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-84,49; 266,42</t>
+          <t>-83,75; 256,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-73,33; 250,78</t>
+          <t>-72,82; 321,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-38,62; 618,61</t>
+          <t>-34,19; 566,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,18; 310,59</t>
+          <t>-39,25; 337,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,91; 235,23</t>
+          <t>-33,03; 254,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,24; 167,35</t>
+          <t>-37,6; 193,93</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,54</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,21</t>
+          <t>-0,79; 2,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,83</t>
+          <t>-0,43; 2,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,57</t>
+          <t>-2,36; 2,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,22</t>
+          <t>-2,46; 1,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,78</t>
+          <t>-1,08; 1,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,48</t>
+          <t>-0,81; 1,92</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>132,71%</t>
+          <t>143,27%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-24,52%</t>
+          <t>-3,29%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-75,33; 701,75</t>
+          <t>-74,12; 847,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-65,52; 990,02</t>
+          <t>-51,17; 1006,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,85; 144,98</t>
+          <t>-62,37; 147,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-68,64; 76,14</t>
+          <t>-53,24; 118,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,53; 146,07</t>
+          <t>-45,57; 171,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,35; 117,02</t>
+          <t>-32,53; 171,33</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-0,32</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>1,67</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,71</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 1,2</t>
+          <t>-5,9; 1,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 2,26</t>
+          <t>-3,96; 2,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 0,44</t>
+          <t>-4,63; 0,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 3,89</t>
+          <t>-1,56; 3,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 0,33</t>
+          <t>-3,62; 0,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,65</t>
+          <t>-1,57; 2,31</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-5,46%</t>
+          <t>-12,55%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107,6%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 208,98</t>
+          <t>-100,0; 192,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-78,08; 243,59</t>
+          <t>-82,96; 299,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-44,6; 727,87</t>
+          <t>-48,02; 775,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-91,05; 76,08</t>
+          <t>-91,17; 76,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-45,92; 268,07</t>
+          <t>-44,61; 264,4</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,2</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,0</t>
+          <t>-3,23; -0,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,51</t>
+          <t>-0,93; 3,25</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,75</t>
+          <t>-2,25; 0,7</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,68</t>
+          <t>-0,81; 2,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,11</t>
+          <t>-2,28; 0,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,56</t>
+          <t>-0,39; 2,53</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 734,8</t>
+          <t>-42,43; 667,4</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1502,17 +1502,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-50,43; 751,14</t>
+          <t>-46,04; 722,02</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 57,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 449,77</t>
+          <t>-21,15; 384,31</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1,51</t>
+          <t>-1,17</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,83</t>
+          <t>-0,93; 0,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,45</t>
+          <t>0,61; 3,25</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,33</t>
+          <t>-2,29; 1,31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -0,06</t>
+          <t>-2,94; 0,15</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,82</t>
+          <t>-1,19; 0,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,17</t>
+          <t>-0,7; 1,28</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>259,69%</t>
+          <t>244,83%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-54,55%</t>
+          <t>-42,15%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-80,56; 302,3</t>
+          <t>-80,98; 335,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>36,44; 1227,77</t>
+          <t>22,2; 1119,2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-63,1; 70,99</t>
+          <t>-60,01; 78,59</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-83,31; -6,73</t>
+          <t>-72,49; 11,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-56,72; 66,86</t>
+          <t>-52,5; 68,65</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-44,08; 91,52</t>
+          <t>-31,56; 110,89</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,29</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,65</t>
+          <t>-1,2; 0,7</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,73</t>
+          <t>-0,12; 2,23</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,98</t>
+          <t>-0,79; 1,92</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,97</t>
+          <t>0,12; 2,75</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,98</t>
+          <t>-0,68; 1,04</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,93</t>
+          <t>0,4; 2,2</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>114,29%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>100,47%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-83,88; 141,15</t>
+          <t>-84,26; 153,7</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 309,74</t>
+          <t>-21,11; 390,9</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 198,91</t>
+          <t>-37,87; 224,9</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 303,15</t>
+          <t>1,68; 263,42</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-39,68; 110,05</t>
+          <t>-39,1; 126,83</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 211,0</t>
+          <t>19,4; 260,54</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,24</t>
+          <t>-0,74; 0,22</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,49</t>
+          <t>0,36; 1,54</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,69</t>
+          <t>-0,76; 0,74</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,74</t>
+          <t>-0,38; 0,85</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,3</t>
+          <t>-0,57; 0,28</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,92</t>
+          <t>0,22; 1,07</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-52,97; 30,24</t>
+          <t>-51,9; 28,49</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>20,82; 175,9</t>
+          <t>24,85; 175,55</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 41,74</t>
+          <t>-32,14; 45,22</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 43,4</t>
+          <t>-16,43; 50,95</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 22,78</t>
+          <t>-31,67; 21,13</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,41; 65,89</t>
+          <t>11,23; 79,32</t>
         </is>
       </c>
     </row>
